--- a/B_Data/Raw_data/Data_pre.xlsx
+++ b/B_Data/Raw_data/Data_pre.xlsx
@@ -12,7 +12,8 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Quarterly" sheetId="1" r:id="rId1"/>
+    <sheet name="Monthly" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
   <si>
     <t>Date</t>
   </si>
@@ -39,6 +40,9 @@
   </si>
   <si>
     <t>HH_2002Q4</t>
+  </si>
+  <si>
+    <t>HH_loan_rates</t>
   </si>
 </sst>
 </file>
@@ -88,11 +92,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -384,7 +389,8 @@
     <col min="2" max="3" width="8.81640625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.1796875" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.08984375" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="8.7265625" style="2"/>
+    <col min="6" max="6" width="10.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -3674,6 +3680,2932 @@
       </c>
       <c r="C215" s="2">
         <v>30.042999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"Times New Roman,Regular"&amp;12&amp;K000000Central Bank of Ireland - UNRESTRICTED</oddHeader>
+    <evenHeader>&amp;L&amp;"Times New Roman,Regular"&amp;12&amp;K000000Central Bank of Ireland - UNRESTRICTED</evenHeader>
+    <firstHeader>&amp;L&amp;"Times New Roman,Regular"&amp;12&amp;K000000Central Bank of Ireland - UNRESTRICTED</firstHeader>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
+  <dimension ref="A1:B363"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="4">
+        <v>27546</v>
+      </c>
+      <c r="B2" s="2">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
+        <v>27576</v>
+      </c>
+      <c r="B3" s="2">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>27607</v>
+      </c>
+      <c r="B4" s="2">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>27638</v>
+      </c>
+      <c r="B5" s="2">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>27668</v>
+      </c>
+      <c r="B6" s="2">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>27699</v>
+      </c>
+      <c r="B7" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>27729</v>
+      </c>
+      <c r="B8" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>27760</v>
+      </c>
+      <c r="B9" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>27791</v>
+      </c>
+      <c r="B10" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>27820</v>
+      </c>
+      <c r="B11" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>27851</v>
+      </c>
+      <c r="B12" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
+        <v>27881</v>
+      </c>
+      <c r="B13" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="4">
+        <v>27912</v>
+      </c>
+      <c r="B14" s="2">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
+        <v>27942</v>
+      </c>
+      <c r="B15" s="2">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>27973</v>
+      </c>
+      <c r="B16" s="2">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
+        <v>28004</v>
+      </c>
+      <c r="B17" s="2">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
+        <v>28034</v>
+      </c>
+      <c r="B18" s="2">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
+        <v>28065</v>
+      </c>
+      <c r="B19" s="2">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="4">
+        <v>28095</v>
+      </c>
+      <c r="B20" s="2">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="4">
+        <v>28126</v>
+      </c>
+      <c r="B21" s="2">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="4">
+        <v>28157</v>
+      </c>
+      <c r="B22" s="2">
+        <v>13.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
+        <v>28185</v>
+      </c>
+      <c r="B23" s="2">
+        <v>12.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="4">
+        <v>28216</v>
+      </c>
+      <c r="B24" s="2">
+        <v>12.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
+        <v>28246</v>
+      </c>
+      <c r="B25" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="4">
+        <v>28277</v>
+      </c>
+      <c r="B26" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="4">
+        <v>28307</v>
+      </c>
+      <c r="B27" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="4">
+        <v>28338</v>
+      </c>
+      <c r="B28" s="2">
+        <v>10.75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="4">
+        <v>28369</v>
+      </c>
+      <c r="B29" s="2">
+        <v>10.75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="4">
+        <v>28399</v>
+      </c>
+      <c r="B30" s="2">
+        <v>10.75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="4">
+        <v>28430</v>
+      </c>
+      <c r="B31" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="4">
+        <v>28460</v>
+      </c>
+      <c r="B32" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="4">
+        <v>28491</v>
+      </c>
+      <c r="B33" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="4">
+        <v>28522</v>
+      </c>
+      <c r="B34" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="4">
+        <v>28550</v>
+      </c>
+      <c r="B35" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="4">
+        <v>28581</v>
+      </c>
+      <c r="B36" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="4">
+        <v>28611</v>
+      </c>
+      <c r="B37" s="2">
+        <v>11.75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="4">
+        <v>28642</v>
+      </c>
+      <c r="B38" s="2">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="4">
+        <v>28672</v>
+      </c>
+      <c r="B39" s="2">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="4">
+        <v>28703</v>
+      </c>
+      <c r="B40" s="2">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="4">
+        <v>28734</v>
+      </c>
+      <c r="B41" s="2">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="4">
+        <v>28764</v>
+      </c>
+      <c r="B42" s="2">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="4">
+        <v>28795</v>
+      </c>
+      <c r="B43" s="2">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" s="4">
+        <v>28825</v>
+      </c>
+      <c r="B44" s="2">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="4">
+        <v>28856</v>
+      </c>
+      <c r="B45" s="2">
+        <v>14.324999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="4">
+        <v>28887</v>
+      </c>
+      <c r="B46" s="2">
+        <v>14.324999999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="4">
+        <v>28915</v>
+      </c>
+      <c r="B47" s="2">
+        <v>14.324999999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="4">
+        <v>28946</v>
+      </c>
+      <c r="B48" s="2">
+        <v>14.324999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="4">
+        <v>28976</v>
+      </c>
+      <c r="B49" s="2">
+        <v>14.324999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" s="4">
+        <v>29007</v>
+      </c>
+      <c r="B50" s="2">
+        <v>14.95</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" s="4">
+        <v>29037</v>
+      </c>
+      <c r="B51" s="2">
+        <v>14.95</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" s="4">
+        <v>29068</v>
+      </c>
+      <c r="B52" s="2">
+        <v>14.95</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" s="4">
+        <v>29099</v>
+      </c>
+      <c r="B53" s="2">
+        <v>14.95</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" s="4">
+        <v>29129</v>
+      </c>
+      <c r="B54" s="2">
+        <v>14.95</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" s="4">
+        <v>29160</v>
+      </c>
+      <c r="B55" s="2">
+        <v>14.95</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" s="4">
+        <v>29190</v>
+      </c>
+      <c r="B56" s="2">
+        <v>14.95</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" s="4">
+        <v>29221</v>
+      </c>
+      <c r="B57" s="2">
+        <v>14.95</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" s="4">
+        <v>29252</v>
+      </c>
+      <c r="B58" s="2">
+        <v>14.95</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" s="4">
+        <v>29281</v>
+      </c>
+      <c r="B59" s="2">
+        <v>14.95</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" s="4">
+        <v>29312</v>
+      </c>
+      <c r="B60" s="2">
+        <v>15.324999999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" s="4">
+        <v>29342</v>
+      </c>
+      <c r="B61" s="2">
+        <v>15.324999999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" s="4">
+        <v>29373</v>
+      </c>
+      <c r="B62" s="2">
+        <v>15.324999999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" s="4">
+        <v>29403</v>
+      </c>
+      <c r="B63" s="2">
+        <v>15.074999999999999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" s="4">
+        <v>29434</v>
+      </c>
+      <c r="B64" s="2">
+        <v>15.074999999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" s="4">
+        <v>29465</v>
+      </c>
+      <c r="B65" s="2">
+        <v>14.574999999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" s="4">
+        <v>29495</v>
+      </c>
+      <c r="B66" s="2">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" s="4">
+        <v>29526</v>
+      </c>
+      <c r="B67" s="2">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" s="4">
+        <v>29556</v>
+      </c>
+      <c r="B68" s="2">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" s="4">
+        <v>29587</v>
+      </c>
+      <c r="B69" s="2">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" s="4">
+        <v>29618</v>
+      </c>
+      <c r="B70" s="2">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" s="4">
+        <v>29646</v>
+      </c>
+      <c r="B71" s="2">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" s="4">
+        <v>29677</v>
+      </c>
+      <c r="B72" s="2">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" s="4">
+        <v>29707</v>
+      </c>
+      <c r="B73" s="2">
+        <v>14.074999999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" s="4">
+        <v>29738</v>
+      </c>
+      <c r="B74" s="2">
+        <v>14.074999999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" s="4">
+        <v>29768</v>
+      </c>
+      <c r="B75" s="2">
+        <v>14.775</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" s="4">
+        <v>29799</v>
+      </c>
+      <c r="B76" s="2">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" s="4">
+        <v>29830</v>
+      </c>
+      <c r="B77" s="2">
+        <v>16.25</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" s="4">
+        <v>29860</v>
+      </c>
+      <c r="B78" s="2">
+        <v>16.25</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" s="4">
+        <v>29891</v>
+      </c>
+      <c r="B79" s="2">
+        <v>16.25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" s="4">
+        <v>29921</v>
+      </c>
+      <c r="B80" s="2">
+        <v>16.25</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" s="4">
+        <v>29952</v>
+      </c>
+      <c r="B81" s="2">
+        <v>16.25</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" s="4">
+        <v>29983</v>
+      </c>
+      <c r="B82" s="2">
+        <v>16.25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83" s="4">
+        <v>30011</v>
+      </c>
+      <c r="B83" s="2">
+        <v>16.75</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84" s="4">
+        <v>30042</v>
+      </c>
+      <c r="B84" s="2">
+        <v>16.75</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85" s="4">
+        <v>30072</v>
+      </c>
+      <c r="B85" s="2">
+        <v>16.75</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86" s="4">
+        <v>30103</v>
+      </c>
+      <c r="B86" s="2">
+        <v>16.75</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" s="4">
+        <v>30133</v>
+      </c>
+      <c r="B87" s="2">
+        <v>16.75</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88" s="4">
+        <v>30164</v>
+      </c>
+      <c r="B88" s="2">
+        <v>16.25</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89" s="4">
+        <v>30195</v>
+      </c>
+      <c r="B89" s="2">
+        <v>15.875</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90" s="4">
+        <v>30225</v>
+      </c>
+      <c r="B90" s="2">
+        <v>14.75</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91" s="4">
+        <v>30256</v>
+      </c>
+      <c r="B91" s="2">
+        <v>14.75</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A92" s="4">
+        <v>30286</v>
+      </c>
+      <c r="B92" s="2">
+        <v>13.875</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A93" s="4">
+        <v>30317</v>
+      </c>
+      <c r="B93" s="2">
+        <v>13.875</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A94" s="4">
+        <v>30348</v>
+      </c>
+      <c r="B94" s="2">
+        <v>13.875</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A95" s="4">
+        <v>30376</v>
+      </c>
+      <c r="B95" s="2">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A96" s="4">
+        <v>30407</v>
+      </c>
+      <c r="B96" s="2">
+        <v>14.125</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97" s="4">
+        <v>30437</v>
+      </c>
+      <c r="B97" s="2">
+        <v>14.125</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98" s="4">
+        <v>30468</v>
+      </c>
+      <c r="B98" s="2">
+        <v>14.125</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99" s="4">
+        <v>30498</v>
+      </c>
+      <c r="B99" s="2">
+        <v>13.75</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100" s="4">
+        <v>30529</v>
+      </c>
+      <c r="B100" s="2">
+        <v>13.75</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101" s="4">
+        <v>30560</v>
+      </c>
+      <c r="B101" s="2">
+        <v>13.375</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102" s="4">
+        <v>30590</v>
+      </c>
+      <c r="B102" s="2">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103" s="4">
+        <v>30621</v>
+      </c>
+      <c r="B103" s="2">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104" s="4">
+        <v>30651</v>
+      </c>
+      <c r="B104" s="2">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A105" s="4">
+        <v>30682</v>
+      </c>
+      <c r="B105" s="2">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A106" s="4">
+        <v>30713</v>
+      </c>
+      <c r="B106" s="2">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A107" s="4">
+        <v>30742</v>
+      </c>
+      <c r="B107" s="2">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A108" s="4">
+        <v>30773</v>
+      </c>
+      <c r="B108" s="2">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A109" s="4">
+        <v>30803</v>
+      </c>
+      <c r="B109" s="2">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A110" s="4">
+        <v>30834</v>
+      </c>
+      <c r="B110" s="2">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A111" s="4">
+        <v>30864</v>
+      </c>
+      <c r="B111" s="2">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A112" s="4">
+        <v>30895</v>
+      </c>
+      <c r="B112" s="2">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A113" s="4">
+        <v>30926</v>
+      </c>
+      <c r="B113" s="2">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A114" s="4">
+        <v>30956</v>
+      </c>
+      <c r="B114" s="2">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A115" s="4">
+        <v>30987</v>
+      </c>
+      <c r="B115" s="2">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A116" s="4">
+        <v>31017</v>
+      </c>
+      <c r="B116" s="2">
+        <v>13.25</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A117" s="4">
+        <v>31048</v>
+      </c>
+      <c r="B117" s="2">
+        <v>13.25</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A118" s="4">
+        <v>31079</v>
+      </c>
+      <c r="B118" s="2">
+        <v>13.875</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A119" s="4">
+        <v>31107</v>
+      </c>
+      <c r="B119" s="2">
+        <v>13.875</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A120" s="4">
+        <v>31138</v>
+      </c>
+      <c r="B120" s="2">
+        <v>13.375</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A121" s="4">
+        <v>31168</v>
+      </c>
+      <c r="B121" s="2">
+        <v>13.375</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A122" s="4">
+        <v>31199</v>
+      </c>
+      <c r="B122" s="2">
+        <v>12.425000000000001</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A123" s="4">
+        <v>31229</v>
+      </c>
+      <c r="B123" s="2">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A124" s="4">
+        <v>31260</v>
+      </c>
+      <c r="B124" s="2">
+        <v>11.375</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A125" s="4">
+        <v>31291</v>
+      </c>
+      <c r="B125" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A126" s="4">
+        <v>31321</v>
+      </c>
+      <c r="B126" s="2">
+        <v>10.625</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A127" s="4">
+        <v>31352</v>
+      </c>
+      <c r="B127" s="2">
+        <v>10.625</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A128" s="4">
+        <v>31382</v>
+      </c>
+      <c r="B128" s="2">
+        <v>10.625</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A129" s="4">
+        <v>31413</v>
+      </c>
+      <c r="B129" s="2">
+        <v>11.375</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A130" s="4">
+        <v>31444</v>
+      </c>
+      <c r="B130" s="2">
+        <v>12.35</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A131" s="4">
+        <v>31472</v>
+      </c>
+      <c r="B131" s="2">
+        <v>12.35</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A132" s="4">
+        <v>31503</v>
+      </c>
+      <c r="B132" s="2">
+        <v>12.35</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A133" s="4">
+        <v>31533</v>
+      </c>
+      <c r="B133" s="2">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A134" s="4">
+        <v>31564</v>
+      </c>
+      <c r="B134" s="2">
+        <v>10.875</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A135" s="4">
+        <v>31594</v>
+      </c>
+      <c r="B135" s="2">
+        <v>10.875</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A136" s="4">
+        <v>31625</v>
+      </c>
+      <c r="B136" s="2">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A137" s="4">
+        <v>31656</v>
+      </c>
+      <c r="B137" s="2">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A138" s="4">
+        <v>31686</v>
+      </c>
+      <c r="B138" s="2">
+        <v>11.25</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A139" s="4">
+        <v>31717</v>
+      </c>
+      <c r="B139" s="2">
+        <v>13.125</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A140" s="4">
+        <v>31747</v>
+      </c>
+      <c r="B140" s="2">
+        <v>13.125</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A141" s="4">
+        <v>31778</v>
+      </c>
+      <c r="B141" s="2">
+        <v>13.125</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A142" s="4">
+        <v>31809</v>
+      </c>
+      <c r="B142" s="2">
+        <v>13.125</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A143" s="4">
+        <v>31837</v>
+      </c>
+      <c r="B143" s="2">
+        <v>13.125</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A144" s="4">
+        <v>31868</v>
+      </c>
+      <c r="B144" s="2">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A145" s="4">
+        <v>31898</v>
+      </c>
+      <c r="B145" s="2">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A146" s="4">
+        <v>31929</v>
+      </c>
+      <c r="B146" s="2">
+        <v>12.25</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A147" s="4">
+        <v>31959</v>
+      </c>
+      <c r="B147" s="2">
+        <v>11.625</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A148" s="4">
+        <v>31990</v>
+      </c>
+      <c r="B148" s="2">
+        <v>11.125</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A149" s="4">
+        <v>32021</v>
+      </c>
+      <c r="B149" s="2">
+        <v>10.75</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A150" s="4">
+        <v>32051</v>
+      </c>
+      <c r="B150" s="2">
+        <v>10.375</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A151" s="4">
+        <v>32082</v>
+      </c>
+      <c r="B151" s="2">
+        <v>10.375</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A152" s="4">
+        <v>32112</v>
+      </c>
+      <c r="B152" s="2">
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A153" s="4">
+        <v>32143</v>
+      </c>
+      <c r="B153" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A154" s="4">
+        <v>32174</v>
+      </c>
+      <c r="B154" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A155" s="4">
+        <v>32203</v>
+      </c>
+      <c r="B155" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A156" s="4">
+        <v>32234</v>
+      </c>
+      <c r="B156" s="2">
+        <v>9.625</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A157" s="4">
+        <v>32264</v>
+      </c>
+      <c r="B157" s="2">
+        <v>9.375</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A158" s="4">
+        <v>32295</v>
+      </c>
+      <c r="B158" s="2">
+        <v>9.125</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A159" s="4">
+        <v>32325</v>
+      </c>
+      <c r="B159" s="2">
+        <v>8.875</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A160" s="4">
+        <v>32356</v>
+      </c>
+      <c r="B160" s="2">
+        <v>8.875</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A161" s="4">
+        <v>32387</v>
+      </c>
+      <c r="B161" s="2">
+        <v>8.875</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A162" s="4">
+        <v>32417</v>
+      </c>
+      <c r="B162" s="2">
+        <v>8.875</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A163" s="4">
+        <v>32448</v>
+      </c>
+      <c r="B163" s="2">
+        <v>8.875</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A164" s="4">
+        <v>32478</v>
+      </c>
+      <c r="B164" s="2">
+        <v>8.875</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A165" s="4">
+        <v>32509</v>
+      </c>
+      <c r="B165" s="2">
+        <v>8.875</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A166" s="4">
+        <v>32540</v>
+      </c>
+      <c r="B166" s="2">
+        <v>8.875</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A167" s="4">
+        <v>32568</v>
+      </c>
+      <c r="B167" s="2">
+        <v>8.875</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A168" s="4">
+        <v>32599</v>
+      </c>
+      <c r="B168" s="2">
+        <v>8.875</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A169" s="4">
+        <v>32629</v>
+      </c>
+      <c r="B169" s="2">
+        <v>9.875</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A170" s="4">
+        <v>32660</v>
+      </c>
+      <c r="B170" s="2">
+        <v>9.875</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A171" s="4">
+        <v>32690</v>
+      </c>
+      <c r="B171" s="2">
+        <v>10.875</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A172" s="4">
+        <v>32721</v>
+      </c>
+      <c r="B172" s="2">
+        <v>10.875</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A173" s="4">
+        <v>32752</v>
+      </c>
+      <c r="B173" s="2">
+        <v>10.875</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A174" s="4">
+        <v>32782</v>
+      </c>
+      <c r="B174" s="2">
+        <v>11.375</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A175" s="4">
+        <v>32813</v>
+      </c>
+      <c r="B175" s="2">
+        <v>11.95</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A176" s="4">
+        <v>32843</v>
+      </c>
+      <c r="B176" s="2">
+        <v>11.875</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A177" s="4">
+        <v>32874</v>
+      </c>
+      <c r="B177" s="2">
+        <v>11.875</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A178" s="4">
+        <v>32905</v>
+      </c>
+      <c r="B178" s="2">
+        <v>11.9375</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A179" s="4">
+        <v>32933</v>
+      </c>
+      <c r="B179" s="2">
+        <v>12.35</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A180" s="4">
+        <v>32964</v>
+      </c>
+      <c r="B180" s="2">
+        <v>12.625</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A181" s="4">
+        <v>32994</v>
+      </c>
+      <c r="B181" s="2">
+        <v>12.875</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A182" s="4">
+        <v>33025</v>
+      </c>
+      <c r="B182" s="2">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A183" s="4">
+        <v>33055</v>
+      </c>
+      <c r="B183" s="2">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A184" s="4">
+        <v>33086</v>
+      </c>
+      <c r="B184" s="2">
+        <v>12.05</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A185" s="4">
+        <v>33117</v>
+      </c>
+      <c r="B185" s="2">
+        <v>12.05</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A186" s="4">
+        <v>33147</v>
+      </c>
+      <c r="B186" s="2">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A187" s="4">
+        <v>33178</v>
+      </c>
+      <c r="B187" s="2">
+        <v>11.55</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A188" s="4">
+        <v>33208</v>
+      </c>
+      <c r="B188" s="2">
+        <v>11.55</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A189" s="4">
+        <v>33239</v>
+      </c>
+      <c r="B189" s="2">
+        <v>12.149999999999999</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A190" s="4">
+        <v>33270</v>
+      </c>
+      <c r="B190" s="2">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A191" s="4">
+        <v>33298</v>
+      </c>
+      <c r="B191" s="2">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A192" s="4">
+        <v>33329</v>
+      </c>
+      <c r="B192" s="2">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A193" s="4">
+        <v>33359</v>
+      </c>
+      <c r="B193" s="2">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A194" s="4">
+        <v>33390</v>
+      </c>
+      <c r="B194" s="2">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A195" s="4">
+        <v>33420</v>
+      </c>
+      <c r="B195" s="2">
+        <v>11.475</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A196" s="4">
+        <v>33451</v>
+      </c>
+      <c r="B196" s="2">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A197" s="4">
+        <v>33482</v>
+      </c>
+      <c r="B197" s="2">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A198" s="4">
+        <v>33512</v>
+      </c>
+      <c r="B198" s="2">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A199" s="4">
+        <v>33543</v>
+      </c>
+      <c r="B199" s="2">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A200" s="4">
+        <v>33573</v>
+      </c>
+      <c r="B200" s="2">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A201" s="4">
+        <v>33604</v>
+      </c>
+      <c r="B201" s="2">
+        <v>11.774999999999999</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A202" s="4">
+        <v>33635</v>
+      </c>
+      <c r="B202" s="2">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A203" s="4">
+        <v>33664</v>
+      </c>
+      <c r="B203" s="2">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A204" s="4">
+        <v>33695</v>
+      </c>
+      <c r="B204" s="2">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A205" s="4">
+        <v>33725</v>
+      </c>
+      <c r="B205" s="2">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A206" s="4">
+        <v>33756</v>
+      </c>
+      <c r="B206" s="2">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A207" s="4">
+        <v>33786</v>
+      </c>
+      <c r="B207" s="2">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A208" s="4">
+        <v>33817</v>
+      </c>
+      <c r="B208" s="2">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A209" s="4">
+        <v>33848</v>
+      </c>
+      <c r="B209" s="2">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A210" s="4">
+        <v>33878</v>
+      </c>
+      <c r="B210" s="2">
+        <v>13.024999999999999</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A211" s="4">
+        <v>33909</v>
+      </c>
+      <c r="B211" s="2">
+        <v>13.024999999999999</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A212" s="4">
+        <v>33939</v>
+      </c>
+      <c r="B212" s="2">
+        <v>13.024999999999999</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A213" s="4">
+        <v>33970</v>
+      </c>
+      <c r="B213" s="2">
+        <v>13.024999999999999</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A214" s="4">
+        <v>34001</v>
+      </c>
+      <c r="B214" s="2">
+        <v>14.24</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A215" s="4">
+        <v>34029</v>
+      </c>
+      <c r="B215" s="2">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A216" s="4">
+        <v>34060</v>
+      </c>
+      <c r="B216" s="2">
+        <v>9.875</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A217" s="4">
+        <v>34090</v>
+      </c>
+      <c r="B217" s="2">
+        <v>9.35</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A218" s="4">
+        <v>34121</v>
+      </c>
+      <c r="B218" s="2">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A219" s="4">
+        <v>34151</v>
+      </c>
+      <c r="B219" s="2">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A220" s="4">
+        <v>34182</v>
+      </c>
+      <c r="B220" s="2">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A221" s="4">
+        <v>34213</v>
+      </c>
+      <c r="B221" s="2">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A222" s="4">
+        <v>34243</v>
+      </c>
+      <c r="B222" s="2">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A223" s="4">
+        <v>34274</v>
+      </c>
+      <c r="B223" s="2">
+        <v>7.85</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A224" s="4">
+        <v>34304</v>
+      </c>
+      <c r="B224" s="2">
+        <v>7.85</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A225" s="4">
+        <v>34335</v>
+      </c>
+      <c r="B225" s="2">
+        <v>7.5750000000000002</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A226" s="4">
+        <v>34366</v>
+      </c>
+      <c r="B226" s="2">
+        <v>7.5750000000000002</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A227" s="4">
+        <v>34394</v>
+      </c>
+      <c r="B227" s="2">
+        <v>7.5750000000000002</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A228" s="4">
+        <v>34425</v>
+      </c>
+      <c r="B228" s="2">
+        <v>7.5750000000000002</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A229" s="4">
+        <v>34455</v>
+      </c>
+      <c r="B229" s="2">
+        <v>7.0750000000000002</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A230" s="4">
+        <v>34486</v>
+      </c>
+      <c r="B230" s="2">
+        <v>7.0750000000000002</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A231" s="4">
+        <v>34516</v>
+      </c>
+      <c r="B231" s="2">
+        <v>7.0750000000000002</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A232" s="4">
+        <v>34547</v>
+      </c>
+      <c r="B232" s="2">
+        <v>7.0750000000000002</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A233" s="4">
+        <v>34578</v>
+      </c>
+      <c r="B233" s="2">
+        <v>7.0750000000000002</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A234" s="4">
+        <v>34608</v>
+      </c>
+      <c r="B234" s="2">
+        <v>7.0750000000000002</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A235" s="4">
+        <v>34639</v>
+      </c>
+      <c r="B235" s="2">
+        <v>7.0750000000000002</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A236" s="4">
+        <v>34669</v>
+      </c>
+      <c r="B236" s="2">
+        <v>7.0750000000000002</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A237" s="4">
+        <v>34700</v>
+      </c>
+      <c r="B237" s="2">
+        <v>7.0750000000000002</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A238" s="4">
+        <v>34731</v>
+      </c>
+      <c r="B238" s="2">
+        <v>7.0750000000000002</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A239" s="4">
+        <v>34759</v>
+      </c>
+      <c r="B239" s="2">
+        <v>7.5699999999999994</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A240" s="4">
+        <v>34790</v>
+      </c>
+      <c r="B240" s="2">
+        <v>7.7449999999999992</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A241" s="4">
+        <v>34820</v>
+      </c>
+      <c r="B241" s="2">
+        <v>7.9949999999999992</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A242" s="4">
+        <v>34851</v>
+      </c>
+      <c r="B242" s="2">
+        <v>7.9949999999999992</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A243" s="4">
+        <v>34881</v>
+      </c>
+      <c r="B243" s="2">
+        <v>7.9949999999999992</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A244" s="4">
+        <v>34912</v>
+      </c>
+      <c r="B244" s="2">
+        <v>7.8250000000000002</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A245" s="4">
+        <v>34943</v>
+      </c>
+      <c r="B245" s="2">
+        <v>7.57</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A246" s="4">
+        <v>34973</v>
+      </c>
+      <c r="B246" s="2">
+        <v>7.57</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A247" s="4">
+        <v>35004</v>
+      </c>
+      <c r="B247" s="2">
+        <v>7.57</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A248" s="4">
+        <v>35034</v>
+      </c>
+      <c r="B248" s="2">
+        <v>7.32</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A249" s="4">
+        <v>35065</v>
+      </c>
+      <c r="B249" s="2">
+        <v>7.1749999999999998</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A250" s="4">
+        <v>35096</v>
+      </c>
+      <c r="B250" s="2">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A251" s="4">
+        <v>35125</v>
+      </c>
+      <c r="B251" s="2">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A252" s="4">
+        <v>35156</v>
+      </c>
+      <c r="B252" s="2">
+        <v>6.9950000000000001</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A253" s="4">
+        <v>35186</v>
+      </c>
+      <c r="B253" s="2">
+        <v>6.875</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A254" s="4">
+        <v>35217</v>
+      </c>
+      <c r="B254" s="2">
+        <v>6.875</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A255" s="4">
+        <v>35247</v>
+      </c>
+      <c r="B255" s="2">
+        <v>6.875</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A256" s="4">
+        <v>35278</v>
+      </c>
+      <c r="B256" s="2">
+        <v>6.9749999999999996</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A257" s="4">
+        <v>35309</v>
+      </c>
+      <c r="B257" s="2">
+        <v>7.0250000000000004</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A258" s="4">
+        <v>35339</v>
+      </c>
+      <c r="B258" s="2">
+        <v>7.0250000000000004</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A259" s="4">
+        <v>35370</v>
+      </c>
+      <c r="B259" s="2">
+        <v>7.0250000000000004</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A260" s="4">
+        <v>35400</v>
+      </c>
+      <c r="B260" s="2">
+        <v>7.0250000000000004</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A261" s="4">
+        <v>35431</v>
+      </c>
+      <c r="B261" s="2">
+        <v>7.0250000000000004</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A262" s="4">
+        <v>35462</v>
+      </c>
+      <c r="B262" s="2">
+        <v>7.0250000000000004</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A263" s="4">
+        <v>35490</v>
+      </c>
+      <c r="B263" s="2">
+        <v>7.0250000000000004</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A264" s="4">
+        <v>35521</v>
+      </c>
+      <c r="B264" s="2">
+        <v>7.0250000000000004</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A265" s="4">
+        <v>35551</v>
+      </c>
+      <c r="B265" s="2">
+        <v>7.4749999999999996</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A266" s="4">
+        <v>35582</v>
+      </c>
+      <c r="B266" s="2">
+        <v>7.4749999999999996</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A267" s="4">
+        <v>35612</v>
+      </c>
+      <c r="B267" s="2">
+        <v>7.4749999999999996</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A268" s="4">
+        <v>35643</v>
+      </c>
+      <c r="B268" s="2">
+        <v>7.4749999999999996</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A269" s="4">
+        <v>35674</v>
+      </c>
+      <c r="B269" s="2">
+        <v>7.4749999999999996</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A270" s="4">
+        <v>35704</v>
+      </c>
+      <c r="B270" s="2">
+        <v>7.4749999999999996</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A271" s="4">
+        <v>35735</v>
+      </c>
+      <c r="B271" s="2">
+        <v>7.4749999999999996</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A272" s="4">
+        <v>35765</v>
+      </c>
+      <c r="B272" s="2">
+        <v>7.4749999999999996</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A273" s="4">
+        <v>35796</v>
+      </c>
+      <c r="B273" s="2">
+        <v>7.4749999999999996</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A274" s="4">
+        <v>35827</v>
+      </c>
+      <c r="B274" s="2">
+        <v>7.4749999999999996</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A275" s="4">
+        <v>35855</v>
+      </c>
+      <c r="B275" s="2">
+        <v>7.4749999999999996</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A276" s="4">
+        <v>35886</v>
+      </c>
+      <c r="B276" s="2">
+        <v>7.4749999999999996</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A277" s="4">
+        <v>35916</v>
+      </c>
+      <c r="B277" s="2">
+        <v>7.4749999999999996</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A278" s="4">
+        <v>35947</v>
+      </c>
+      <c r="B278" s="2">
+        <v>7.4749999999999996</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A279" s="4">
+        <v>35977</v>
+      </c>
+      <c r="B279" s="2">
+        <v>7.4749999999999996</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A280" s="4">
+        <v>36008</v>
+      </c>
+      <c r="B280" s="2">
+        <v>7.4749999999999996</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A281" s="4">
+        <v>36039</v>
+      </c>
+      <c r="B281" s="2">
+        <v>7.4749999999999996</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A282" s="4">
+        <v>36069</v>
+      </c>
+      <c r="B282" s="2">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A283" s="4">
+        <v>36100</v>
+      </c>
+      <c r="B283" s="2">
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A284" s="4">
+        <v>36130</v>
+      </c>
+      <c r="B284" s="2">
+        <v>5.9749999999999996</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A285" s="4">
+        <v>36161</v>
+      </c>
+      <c r="B285" s="2">
+        <v>5.5250000000000004</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A286" s="4">
+        <v>36192</v>
+      </c>
+      <c r="B286" s="2">
+        <v>5.5250000000000004</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A287" s="4">
+        <v>36220</v>
+      </c>
+      <c r="B287" s="2">
+        <v>5.5250000000000004</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A288" s="4">
+        <v>36251</v>
+      </c>
+      <c r="B288" s="2">
+        <v>5.1899999999999995</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A289" s="4">
+        <v>36281</v>
+      </c>
+      <c r="B289" s="2">
+        <v>5.17</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A290" s="4">
+        <v>36312</v>
+      </c>
+      <c r="B290" s="2">
+        <v>5.17</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A291" s="4">
+        <v>36342</v>
+      </c>
+      <c r="B291" s="2">
+        <v>5.17</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A292" s="4">
+        <v>36373</v>
+      </c>
+      <c r="B292" s="2">
+        <v>4.74</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A293" s="4">
+        <v>36404</v>
+      </c>
+      <c r="B293" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A294" s="4">
+        <v>36434</v>
+      </c>
+      <c r="B294" s="2">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A295" s="4">
+        <v>36465</v>
+      </c>
+      <c r="B295" s="2">
+        <v>4.04</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A296" s="4">
+        <v>36495</v>
+      </c>
+      <c r="B296" s="2">
+        <v>4.04</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A297" s="4">
+        <v>36526</v>
+      </c>
+      <c r="B297" s="2">
+        <v>4.0449999999999999</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A298" s="4">
+        <v>36557</v>
+      </c>
+      <c r="B298" s="2">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A299" s="4">
+        <v>36586</v>
+      </c>
+      <c r="B299" s="2">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A300" s="4">
+        <v>36617</v>
+      </c>
+      <c r="B300" s="2">
+        <v>4.3250000000000002</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A301" s="4">
+        <v>36647</v>
+      </c>
+      <c r="B301" s="2">
+        <v>4.4450000000000003</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A302" s="4">
+        <v>36678</v>
+      </c>
+      <c r="B302" s="2">
+        <v>5.29</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A303" s="4">
+        <v>36708</v>
+      </c>
+      <c r="B303" s="2">
+        <v>5.29</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A304" s="4">
+        <v>36739</v>
+      </c>
+      <c r="B304" s="2">
+        <v>5.29</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A305" s="4">
+        <v>36770</v>
+      </c>
+      <c r="B305" s="2">
+        <v>5.415</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A306" s="4">
+        <v>36800</v>
+      </c>
+      <c r="B306" s="2">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A307" s="4">
+        <v>36831</v>
+      </c>
+      <c r="B307" s="2">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A308" s="4">
+        <v>36861</v>
+      </c>
+      <c r="B308" s="2">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A309" s="4">
+        <v>36892</v>
+      </c>
+      <c r="B309" s="2">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A310" s="4">
+        <v>36923</v>
+      </c>
+      <c r="B310" s="2">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A311" s="4">
+        <v>36951</v>
+      </c>
+      <c r="B311" s="2">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A312" s="4">
+        <v>36982</v>
+      </c>
+      <c r="B312" s="2">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A313" s="4">
+        <v>37012</v>
+      </c>
+      <c r="B313" s="2">
+        <v>5.6999999999999993</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A314" s="4">
+        <v>37043</v>
+      </c>
+      <c r="B314" s="2">
+        <v>5.5949999999999998</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A315" s="4">
+        <v>37073</v>
+      </c>
+      <c r="B315" s="2">
+        <v>5.5949999999999998</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A316" s="4">
+        <v>37104</v>
+      </c>
+      <c r="B316" s="2">
+        <v>5.5949999999999998</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A317" s="4">
+        <v>37135</v>
+      </c>
+      <c r="B317" s="2">
+        <v>5.4949999999999992</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A318" s="4">
+        <v>37165</v>
+      </c>
+      <c r="B318" s="2">
+        <v>5.1950000000000003</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A319" s="4">
+        <v>37196</v>
+      </c>
+      <c r="B319" s="2">
+        <v>4.7249999999999996</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A320" s="4">
+        <v>37226</v>
+      </c>
+      <c r="B320" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A321" s="4">
+        <v>37257</v>
+      </c>
+      <c r="B321" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A322" s="4">
+        <v>37288</v>
+      </c>
+      <c r="B322" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A323" s="4">
+        <v>37316</v>
+      </c>
+      <c r="B323" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A324" s="4">
+        <v>37347</v>
+      </c>
+      <c r="B324" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A325" s="4">
+        <v>37377</v>
+      </c>
+      <c r="B325" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A326" s="4">
+        <v>37408</v>
+      </c>
+      <c r="B326" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A327" s="4">
+        <v>37438</v>
+      </c>
+      <c r="B327" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A328" s="4">
+        <v>37469</v>
+      </c>
+      <c r="B328" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A329" s="4">
+        <v>37500</v>
+      </c>
+      <c r="B329" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A330" s="4">
+        <v>37530</v>
+      </c>
+      <c r="B330" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A331" s="4">
+        <v>37561</v>
+      </c>
+      <c r="B331" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A332" s="4">
+        <v>37591</v>
+      </c>
+      <c r="B332" s="2">
+        <v>4.2750000000000004</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A333" s="4">
+        <v>37622</v>
+      </c>
+      <c r="B333" s="2">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A334" s="4">
+        <v>37653</v>
+      </c>
+      <c r="B334" s="2">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A335" s="4">
+        <v>37681</v>
+      </c>
+      <c r="B335" s="2">
+        <v>3.8899999999999997</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A336" s="4">
+        <v>37712</v>
+      </c>
+      <c r="B336" s="2">
+        <v>3.8899999999999997</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A337" s="4">
+        <v>37742</v>
+      </c>
+      <c r="B337" s="2">
+        <v>3.8899999999999997</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A338" s="4">
+        <v>37773</v>
+      </c>
+      <c r="B338" s="2">
+        <v>3.5249999999999999</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A339" s="4">
+        <v>37803</v>
+      </c>
+      <c r="B339" s="2">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A340" s="4">
+        <v>37834</v>
+      </c>
+      <c r="B340" s="2">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A341" s="4">
+        <v>37865</v>
+      </c>
+      <c r="B341" s="2">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A342" s="4">
+        <v>37895</v>
+      </c>
+      <c r="B342" s="2">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A343" s="4">
+        <v>37926</v>
+      </c>
+      <c r="B343" s="2">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A344" s="4">
+        <v>37956</v>
+      </c>
+      <c r="B344" s="2">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A345" s="4">
+        <v>37987</v>
+      </c>
+      <c r="B345" s="2">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A346" s="4">
+        <v>38018</v>
+      </c>
+      <c r="B346" s="2">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A347" s="4">
+        <v>38047</v>
+      </c>
+      <c r="B347" s="2">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A348" s="4">
+        <v>38078</v>
+      </c>
+      <c r="B348" s="2">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A349" s="4">
+        <v>38108</v>
+      </c>
+      <c r="B349" s="2">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A350" s="4">
+        <v>38139</v>
+      </c>
+      <c r="B350" s="2">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A351" s="4">
+        <v>38169</v>
+      </c>
+      <c r="B351" s="2">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A352" s="4">
+        <v>38200</v>
+      </c>
+      <c r="B352" s="2">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A353" s="4">
+        <v>38231</v>
+      </c>
+      <c r="B353" s="2">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A354" s="4">
+        <v>38261</v>
+      </c>
+      <c r="B354" s="2">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A355" s="4">
+        <v>38292</v>
+      </c>
+      <c r="B355" s="2">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A356" s="4">
+        <v>38322</v>
+      </c>
+      <c r="B356" s="2">
+        <v>3.4249999999999998</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A357" s="4">
+        <v>38353</v>
+      </c>
+      <c r="B357" s="2">
+        <v>3.4249999999999998</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A358" s="4">
+        <v>38384</v>
+      </c>
+      <c r="B358" s="2">
+        <v>3.4249999999999998</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A359" s="4">
+        <v>38412</v>
+      </c>
+      <c r="B359" s="2">
+        <v>3.4249999999999998</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A360" s="4">
+        <v>38443</v>
+      </c>
+      <c r="B360" s="2">
+        <v>3.4249999999999998</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A361" s="4">
+        <v>38473</v>
+      </c>
+      <c r="B361" s="2">
+        <v>3.4249999999999998</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A362" s="4">
+        <v>38504</v>
+      </c>
+      <c r="B362" s="2">
+        <v>3.4249999999999998</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A363" s="4">
+        <v>38534</v>
+      </c>
+      <c r="B363" s="2">
+        <v>3.4249999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -3694,7 +6626,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A1F67EB-82E5-4F5B-83F5-B5012FBA5FE0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29732DF0-E7F0-4D32-AE54-787A43302137}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>

--- a/B_Data/Raw_data/Data_pre.xlsx
+++ b/B_Data/Raw_data/Data_pre.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fmugrabi\Desktop\House_credit_cycles\B_Data\Raw_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fmugrabi\Desktop\House_credit_cycles-main\B_Data\Raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5310"/>
   </bookViews>
   <sheets>
     <sheet name="Quarterly" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>Date</t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t>HH_loan_rates</t>
+  </si>
+  <si>
+    <t>GDP_pre_1997</t>
   </si>
 </sst>
 </file>
@@ -92,12 +95,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -382,18 +386,18 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:E215"/>
+  <dimension ref="A1:F215"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="8.81640625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.1796875" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.08984375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.1796875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -409,8 +413,11 @@
       <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>26114</v>
       </c>
@@ -423,8 +430,11 @@
       <c r="D2" s="2">
         <v>2.3514110993723203</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F2" s="5">
+        <v>626.97775153812688</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>26206</v>
       </c>
@@ -437,8 +447,11 @@
       <c r="D3" s="2">
         <v>2.4296610527624138</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F3" s="5">
+        <v>626.97775153812688</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>26298</v>
       </c>
@@ -451,8 +464,11 @@
       <c r="D4" s="2">
         <v>2.5079110061525074</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F4" s="5">
+        <v>626.97775153812688</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>26389</v>
       </c>
@@ -465,8 +481,11 @@
       <c r="D5" s="2">
         <v>2.6428921757504193</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F5" s="5">
+        <v>761.95892113603884</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>26480</v>
       </c>
@@ -479,8 +498,11 @@
       <c r="D6" s="2">
         <v>2.7778733453483313</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F6" s="5">
+        <v>761.95892113603884</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>26572</v>
       </c>
@@ -493,8 +515,11 @@
       <c r="D7" s="2">
         <v>2.9128545149462433</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F7" s="5">
+        <v>761.95892113603884</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>26664</v>
       </c>
@@ -507,8 +532,11 @@
       <c r="D8" s="2">
         <v>3.0478356845441552</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F8" s="5">
+        <v>761.95892113603884</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>26754</v>
       </c>
@@ -521,8 +549,11 @@
       <c r="D9" s="2">
         <v>3.206047309054751</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F9" s="5">
+        <v>920.17054564663476</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>26845</v>
       </c>
@@ -535,8 +566,11 @@
       <c r="D10" s="2">
         <v>3.3642589335653468</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F10" s="5">
+        <v>920.17054564663476</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>26937</v>
       </c>
@@ -549,8 +583,11 @@
       <c r="D11" s="2">
         <v>3.5224705580759434</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F11" s="5">
+        <v>920.17054564663476</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>27029</v>
       </c>
@@ -563,8 +600,11 @@
       <c r="D12" s="2">
         <v>3.6806821825865392</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F12" s="5">
+        <v>920.17054564663476</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>27119</v>
       </c>
@@ -577,8 +617,11 @@
       <c r="D13" s="2">
         <v>3.782896184202349</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F13" s="5">
+        <v>1022.3845472624449</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>27210</v>
       </c>
@@ -591,8 +634,11 @@
       <c r="D14" s="2">
         <v>3.8851101858181591</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F14" s="5">
+        <v>1022.3845472624449</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>27302</v>
       </c>
@@ -605,8 +651,11 @@
       <c r="D15" s="2">
         <v>3.9873241874339693</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F15" s="5">
+        <v>1022.3845472624449</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>27394</v>
       </c>
@@ -619,8 +668,11 @@
       <c r="D16" s="2">
         <v>4.0895381890497795</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F16" s="5">
+        <v>1022.3845472624449</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>27484</v>
       </c>
@@ -636,8 +688,11 @@
       <c r="E17" s="2">
         <v>5.3870716646142434</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F17" s="5">
+        <v>1285.5000155366354</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>27575</v>
       </c>
@@ -653,8 +708,11 @@
       <c r="E18" s="2">
         <v>5.8174849956472974</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F18" s="5">
+        <v>1285.5000155366354</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>27667</v>
       </c>
@@ -670,8 +728,11 @@
       <c r="E19" s="2">
         <v>6.0131274188441415</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F19" s="5">
+        <v>1285.5000155366354</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>27759</v>
       </c>
@@ -687,8 +748,11 @@
       <c r="E20" s="2">
         <v>6.2956580946960532</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F20" s="5">
+        <v>1285.5000155366354</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>27850</v>
       </c>
@@ -704,8 +768,11 @@
       <c r="E21" s="2">
         <v>6.6788870766051627</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F21" s="5">
+        <v>1583.5834317320241</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>27941</v>
       </c>
@@ -721,8 +788,11 @@
       <c r="E22" s="2">
         <v>6.9107808899825969</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F22" s="5">
+        <v>1583.5834317320241</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>28033</v>
       </c>
@@ -738,8 +808,11 @@
       <c r="E23" s="2">
         <v>7.0465797484368764</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F23" s="5">
+        <v>1583.5834317320241</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>28125</v>
       </c>
@@ -755,8 +828,11 @@
       <c r="E24" s="2">
         <v>7.7629762686723742</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F24" s="5">
+        <v>1583.5834317320241</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>28215</v>
       </c>
@@ -772,8 +848,11 @@
       <c r="E25" s="2">
         <v>7.7716075520487049</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F25" s="5">
+        <v>1927.638695544093</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>28306</v>
       </c>
@@ -789,8 +868,11 @@
       <c r="E26" s="2">
         <v>8.2319426654530403</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F26" s="5">
+        <v>1927.638695544093</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>28398</v>
       </c>
@@ -806,8 +888,11 @@
       <c r="E27" s="2">
         <v>8.8079369761002173</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F27" s="5">
+        <v>1927.638695544093</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>28490</v>
       </c>
@@ -823,8 +908,11 @@
       <c r="E28" s="2">
         <v>9.082411787467553</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F28" s="5">
+        <v>1927.638695544093</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>28580</v>
       </c>
@@ -840,8 +928,11 @@
       <c r="E29" s="2">
         <v>10.145785899431571</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F29" s="5">
+        <v>2278.0517680691069</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>28671</v>
       </c>
@@ -857,8 +948,11 @@
       <c r="E30" s="2">
         <v>10.997405859229589</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F30" s="5">
+        <v>2278.0517680691069</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>28763</v>
       </c>
@@ -874,8 +968,11 @@
       <c r="E31" s="2">
         <v>11.371428138870614</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F31" s="5">
+        <v>2278.0517680691069</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>28855</v>
       </c>
@@ -891,8 +988,11 @@
       <c r="E32" s="2">
         <v>11.343232613174598</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F32" s="5">
+        <v>2278.0517680691069</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>28945</v>
       </c>
@@ -908,8 +1008,11 @@
       <c r="E33" s="2">
         <v>12.315690540241258</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F33" s="5">
+        <v>2698.6452675408614</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>29036</v>
       </c>
@@ -925,8 +1028,11 @@
       <c r="E34" s="2">
         <v>13.737550621768902</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F34" s="5">
+        <v>2698.6452675408614</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>29128</v>
       </c>
@@ -942,8 +1048,11 @@
       <c r="E35" s="2">
         <v>13.704176326047088</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F35" s="5">
+        <v>2698.6452675408614</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>29220</v>
       </c>
@@ -959,8 +1068,11 @@
       <c r="E36" s="2">
         <v>13.630522707902394</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F36" s="5">
+        <v>2698.6452675408614</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>29311</v>
       </c>
@@ -976,8 +1088,11 @@
       <c r="E37" s="2">
         <v>14.733600723397537</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F37" s="5">
+        <v>3004.3807022978635</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>29402</v>
       </c>
@@ -993,8 +1108,11 @@
       <c r="E38" s="2">
         <v>15.462081040359896</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F38" s="5">
+        <v>3449.3070027636409</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>29494</v>
       </c>
@@ -1010,8 +1128,11 @@
       <c r="E39" s="2">
         <v>16.276874191085572</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F39" s="5">
+        <v>3447.6494033639028</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>29586</v>
       </c>
@@ -1027,8 +1148,11 @@
       <c r="E40" s="2">
         <v>17.058868464981185</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F40" s="5">
+        <v>3613.9617136984311</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>29676</v>
       </c>
@@ -1044,8 +1168,11 @@
       <c r="E41" s="2">
         <v>17.477773418179137</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F41" s="5">
+        <v>3825.9776453086524</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>29767</v>
       </c>
@@ -1061,8 +1188,11 @@
       <c r="E42" s="2">
         <v>18.026723040913804</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F42" s="5">
+        <v>4006.5080310953867</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>29859</v>
       </c>
@@ -1078,8 +1208,11 @@
       <c r="E43" s="2">
         <v>18.656806727385987</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F43" s="5">
+        <v>4012.0222187646232</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>29951</v>
       </c>
@@ -1095,8 +1228,11 @@
       <c r="E44" s="2">
         <v>19.161449095455492</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F44" s="5">
+        <v>4494.1740503740411</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>30041</v>
       </c>
@@ -1112,8 +1248,11 @@
       <c r="E45" s="2">
         <v>19.54122556401407</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F45" s="5">
+        <v>4423.6553521848855</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>30132</v>
       </c>
@@ -1129,8 +1268,11 @@
       <c r="E46" s="2">
         <v>20.048169607650596</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F46" s="5">
+        <v>4933.162762914324</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
         <v>30224</v>
       </c>
@@ -1146,8 +1288,11 @@
       <c r="E47" s="2">
         <v>19.973940570614147</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F47" s="5">
+        <v>4885.8001788213842</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
         <v>30316</v>
       </c>
@@ -1163,8 +1308,11 @@
       <c r="E48" s="2">
         <v>20.25474498979079</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F48" s="5">
+        <v>5250.110439896428</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
         <v>30406</v>
       </c>
@@ -1180,8 +1328,11 @@
       <c r="E49" s="2">
         <v>20.221370694068973</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F49" s="5">
+        <v>5101.2841880357837</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
         <v>30497</v>
       </c>
@@ -1197,8 +1348,11 @@
       <c r="E50" s="2">
         <v>20.094203118991029</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F50" s="5">
+        <v>5322.5483808590852</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
         <v>30589</v>
       </c>
@@ -1214,8 +1368,11 @@
       <c r="E51" s="2">
         <v>20.41873937394109</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F51" s="5">
+        <v>5285.5714865949631</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
         <v>30681</v>
       </c>
@@ -1231,8 +1388,11 @@
       <c r="E52" s="2">
         <v>19.837566293268114</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F52" s="5">
+        <v>5640.0872864207158</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
         <v>30772</v>
       </c>
@@ -1248,8 +1408,11 @@
       <c r="E53" s="2">
         <v>20.400901388296671</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F53" s="5">
+        <v>5439.3709515613737</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="3">
         <v>30863</v>
       </c>
@@ -1265,8 +1428,11 @@
       <c r="E54" s="2">
         <v>20.6161080538132</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F54" s="5">
+        <v>6182.4934621253024</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
         <v>30955</v>
       </c>
@@ -1282,8 +1448,11 @@
       <c r="E55" s="2">
         <v>20.774923667937692</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F55" s="5">
+        <v>5822.0301484112233</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="3">
         <v>31047</v>
       </c>
@@ -1299,8 +1468,11 @@
       <c r="E56" s="2">
         <v>20.598270068168777</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F56" s="5">
+        <v>6145.0936849929185</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
         <v>31137</v>
       </c>
@@ -1316,8 +1488,11 @@
       <c r="E57" s="2">
         <v>20.695515860875442</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F57" s="5">
+        <v>6069.8020786079787</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="3">
         <v>31228</v>
       </c>
@@ -1333,8 +1508,11 @@
       <c r="E58" s="2">
         <v>21.029258818093592</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F58" s="5">
+        <v>6451.878528822348</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="3">
         <v>31320</v>
       </c>
@@ -1350,8 +1528,11 @@
       <c r="E59" s="2">
         <v>21.134560475284829</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F59" s="5">
+        <v>6350.3669489765962</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="3">
         <v>31412</v>
       </c>
@@ -1367,8 +1548,11 @@
       <c r="E60" s="2">
         <v>21.611582736550073</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F60" s="5">
+        <v>6592.2850484753617</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="3">
         <v>31502</v>
       </c>
@@ -1384,8 +1568,11 @@
       <c r="E61" s="2">
         <v>21.390621882115994</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F61" s="5">
+        <v>6672.7786560756631</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="3">
         <v>31593</v>
       </c>
@@ -1401,8 +1588,11 @@
       <c r="E62" s="2">
         <v>21.921733519206242</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F62" s="5">
+        <v>6758.7820425494056</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="3">
         <v>31685</v>
       </c>
@@ -1418,8 +1608,11 @@
       <c r="E63" s="2">
         <v>22.219225086243796</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F63" s="5">
+        <v>6723.3721350759779</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="3">
         <v>31777</v>
       </c>
@@ -1435,8 +1628,11 @@
       <c r="E64" s="2">
         <v>21.911375979154641</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F64" s="5">
+        <v>6939.660504850548</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="3">
         <v>31867</v>
       </c>
@@ -1452,8 +1648,11 @@
       <c r="E65" s="2">
         <v>21.749683270571374</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F65" s="5">
+        <v>6811.9520171627091</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="3">
         <v>31958</v>
       </c>
@@ -1469,8 +1668,11 @@
       <c r="E66" s="2">
         <v>21.517789457193942</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F66" s="5">
+        <v>7349.6867700291168</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="3">
         <v>32050</v>
       </c>
@@ -1486,8 +1688,11 @@
       <c r="E67" s="2">
         <v>22.181247439387935</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F67" s="5">
+        <v>7116.0826869874409</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="3">
         <v>32142</v>
       </c>
@@ -1503,8 +1708,11 @@
       <c r="E68" s="2">
         <v>23.343593600733886</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F68" s="5">
+        <v>7591.1481411214218</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="3">
         <v>32233</v>
       </c>
@@ -1520,8 +1728,11 @@
       <c r="E69" s="2">
         <v>23.121481908516294</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F69" s="5">
+        <v>7318.7614718446339</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="3">
         <v>32324</v>
       </c>
@@ -1537,8 +1748,11 @@
       <c r="E70" s="2">
         <v>23.124934421866829</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F70" s="5">
+        <v>7691.0454046827035</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="3">
         <v>32416</v>
       </c>
@@ -1554,8 +1768,11 @@
       <c r="E71" s="2">
         <v>23.864923116664301</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F71" s="5">
+        <v>7726.0362598445017</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="3">
         <v>32508</v>
       </c>
@@ -1571,8 +1788,11 @@
       <c r="E72" s="2">
         <v>24.664755376204329</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F72" s="5">
+        <v>7970.612528163394</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="3">
         <v>32598</v>
       </c>
@@ -1588,8 +1808,11 @@
       <c r="E73" s="2">
         <v>25.76092836499841</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F73" s="5">
+        <v>7937.6607545582274</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="3">
         <v>32689</v>
       </c>
@@ -1605,8 +1828,11 @@
       <c r="E74" s="2">
         <v>25.356984302986103</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F74" s="5">
+        <v>8447.9542009291454</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="3">
         <v>32781</v>
       </c>
@@ -1622,8 +1848,11 @@
       <c r="E75" s="2">
         <v>26.544648895569289</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F75" s="5">
+        <v>8531.8709524819642</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="3">
         <v>32873</v>
       </c>
@@ -1639,8 +1868,11 @@
       <c r="E76" s="2">
         <v>28.302553609882104</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F76" s="5">
+        <v>8898.1945989934757</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="3">
         <v>32963</v>
       </c>
@@ -1656,8 +1888,11 @@
       <c r="E77" s="2">
         <v>29.622564547569031</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F77" s="5">
+        <v>8888.1885733893905</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="3">
         <v>33054</v>
       </c>
@@ -1673,8 +1908,11 @@
       <c r="E78" s="2">
         <v>29.32046962939744</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F78" s="5">
+        <v>9560.6623098195741</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="3">
         <v>33146</v>
       </c>
@@ -1690,8 +1928,11 @@
       <c r="E79" s="2">
         <v>30.25955326074228</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F79" s="5">
+        <v>9098.9756710721558</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="3">
         <v>33238</v>
       </c>
@@ -1707,8 +1948,11 @@
       <c r="E80" s="2">
         <v>29.649033816589782</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F80" s="5">
+        <v>9440.5112146887277</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="3">
         <v>33328</v>
       </c>
@@ -1724,8 +1968,11 @@
       <c r="E81" s="2">
         <v>30.366005755717033</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F81" s="5">
+        <v>9240.1322289973214</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="3">
         <v>33419</v>
       </c>
@@ -1741,8 +1988,11 @@
       <c r="E82" s="2">
         <v>29.44476011001661</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F82" s="5">
+        <v>9717.0597808576786</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="3">
         <v>33511</v>
       </c>
@@ -1758,8 +2008,11 @@
       <c r="E83" s="2">
         <v>30.224452708345201</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F83" s="5">
+        <v>9562.1268758107581</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="3">
         <v>33603</v>
       </c>
@@ -1775,8 +2028,11 @@
       <c r="E84" s="2">
         <v>31.301061454819596</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F84" s="5">
+        <v>9907.6302202876377</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="3">
         <v>33694</v>
       </c>
@@ -1792,8 +2048,11 @@
       <c r="E85" s="2">
         <v>31.581290455104483</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F85" s="5">
+        <v>9758.9360048923118</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="3">
         <v>33785</v>
       </c>
@@ -1809,8 +2068,11 @@
       <c r="E86" s="2">
         <v>31.162385501906538</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F86" s="5">
+        <v>10533.045434322765</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="3">
         <v>33877</v>
       </c>
@@ -1826,8 +2088,11 @@
       <c r="E87" s="2">
         <v>31.394279315283967</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F87" s="5">
+        <v>10117.161976383253</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="3">
         <v>33969</v>
       </c>
@@ -1843,8 +2108,11 @@
       <c r="E88" s="2">
         <v>31.436860313273872</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F88" s="5">
+        <v>10403.233623219066</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="3">
         <v>34059</v>
       </c>
@@ -1860,8 +2128,11 @@
       <c r="E89" s="2">
         <v>30.80505037012642</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F89" s="5">
+        <v>10330.80016547462</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="3">
         <v>34150</v>
       </c>
@@ -1877,8 +2148,11 @@
       <c r="E90" s="2">
         <v>31.702128422373121</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F90" s="5">
+        <v>11302.629427759271</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="3">
         <v>34242</v>
       </c>
@@ -1894,8 +2168,11 @@
       <c r="E91" s="2">
         <v>32.155558509076393</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F91" s="5">
+        <v>10836.019605288488</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="3">
         <v>34334</v>
       </c>
@@ -1911,8 +2188,11 @@
       <c r="E92" s="2">
         <v>31.610636818584009</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F92" s="5">
+        <v>11553.733097576212</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="3">
         <v>34424</v>
       </c>
@@ -1928,8 +2208,11 @@
       <c r="E93" s="2">
         <v>33.089463370395443</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F93" s="5">
+        <v>11157.715787163232</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="3">
         <v>34515</v>
       </c>
@@ -1945,8 +2228,11 @@
       <c r="E94" s="2">
         <v>32.667105903846959</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F94" s="5">
+        <v>11845.928618073274</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="3">
         <v>34607</v>
       </c>
@@ -1962,8 +2248,11 @@
       <c r="E95" s="2">
         <v>32.145200969024792</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F95" s="5">
+        <v>11852.738501472433</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="3">
         <v>34699</v>
       </c>
@@ -1979,8 +2268,11 @@
       <c r="E96" s="2">
         <v>33.98711684153389</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F96" s="5">
+        <v>12457.089886197118</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="3">
         <v>34789</v>
       </c>
@@ -1996,8 +2288,11 @@
       <c r="E97" s="2">
         <v>35.22599371548332</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F97" s="5">
+        <v>13152</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="3">
         <v>34880</v>
       </c>
@@ -2013,8 +2308,11 @@
       <c r="E98" s="2">
         <v>34.738613914166471</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F98" s="5">
+        <v>13940</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="3">
         <v>34972</v>
       </c>
@@ -2030,8 +2328,11 @@
       <c r="E99" s="2">
         <v>34.98892113208008</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F99" s="5">
+        <v>13604</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="3">
         <v>35064</v>
       </c>
@@ -2047,8 +2348,11 @@
       <c r="E100" s="2">
         <v>36.391792390179795</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F100" s="5">
+        <v>14063</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="3">
         <v>35155</v>
       </c>
@@ -2064,8 +2368,11 @@
       <c r="E101" s="2">
         <v>36.966060444151708</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F101" s="5">
+        <v>14611</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="3">
         <v>35246</v>
       </c>
@@ -2081,8 +2388,11 @@
       <c r="E102" s="2">
         <v>38.08714754278509</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F102" s="5">
+        <v>15268</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="3">
         <v>35338</v>
       </c>
@@ -2098,8 +2408,11 @@
       <c r="E103" s="2">
         <v>39.10290646560712</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F103" s="5">
+        <v>14752</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="3">
         <v>35430</v>
       </c>
@@ -2115,8 +2428,11 @@
       <c r="E104" s="2">
         <v>39.100318329883464</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F104" s="5">
+        <v>15516</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="3">
         <v>35520</v>
       </c>
@@ -2132,8 +2448,11 @@
       <c r="E105" s="2">
         <v>41.76006259047945</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F105" s="5">
+        <v>16112</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="3">
         <v>35611</v>
       </c>
@@ -2149,8 +2468,11 @@
       <c r="E106" s="2">
         <v>43.204297971722482</v>
       </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F106" s="2">
+        <v>17360</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="3">
         <v>35703</v>
       </c>
@@ -2166,8 +2488,11 @@
       <c r="E107" s="2">
         <v>44.519324190642656</v>
       </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F107" s="2">
+        <v>17388</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="3">
         <v>35795</v>
       </c>
@@ -2183,8 +2508,11 @@
       <c r="E108" s="2">
         <v>46.301358429297025</v>
       </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F108" s="2">
+        <v>18540</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="3">
         <v>35885</v>
       </c>
@@ -2201,7 +2529,7 @@
         <v>48.547522636820354</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="3">
         <v>35976</v>
       </c>
@@ -2215,7 +2543,7 @@
         <v>52.797199439525912</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="3">
         <v>36068</v>
       </c>
@@ -2229,7 +2557,7 @@
         <v>56.917297341241238</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="3">
         <v>36160</v>
       </c>
@@ -6626,7 +6954,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29732DF0-E7F0-4D32-AE54-787A43302137}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B607CB7C-3013-418C-9FD6-30F5E0A9807A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
